--- a/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="503">
   <si>
     <t>S.No.</t>
   </si>
@@ -90,10 +90,13 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Extends the existing TST_LAND_TC_5 (hero heading/sub-heading/buttons/logo) with the header and footer items — a new function, not a duplicate.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
+    <t>Verified on Production: header logo/home link, language switcher, login/signup buttons, heading text, and all footer links are visible.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 1)</t>
   </si>
   <si>
     <t>Automate</t>
@@ -120,6 +123,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LAND_TC_3 already clicks Log in and checks the login page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking Log in navigates to the login page (/login).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 2, Suite 3)</t>
+  </si>
+  <si>
     <t>TST_LAND_TC_2</t>
   </si>
   <si>
@@ -136,6 +145,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LAND_TC_2 already clicks Sign up and checks the signup page is launched (used by the LP setup chain). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Sign up opens the role selection screen (/regoptions).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 4, Suite 5)</t>
   </si>
   <si>
     <t>TST_LAND_TC_7</t>
@@ -164,6 +179,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. The existing TST_LAND_TC_4 only opens the dropdown (asserts the click); this case asserts the outcome. Automation reuses LAND_TC_4 for the click.</t>
   </si>
   <si>
+    <t>Verified on Production: language switcher expands, changes language to Español, and reverts back to English.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_1</t>
   </si>
   <si>
@@ -182,6 +200,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Source row split one case per link. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_1 already clicks the link and checks the page is launched (footer.test.js, active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Terms of use page opens with expected heading in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_2</t>
   </si>
   <si>
@@ -197,6 +218,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_2 already clicks the link and checks the page is launched (active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Privacy notice page opens with expected heading in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_3</t>
   </si>
   <si>
@@ -212,6 +236,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_3 already clicks the link and checks the page is launched (active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Accessibility page opens with expected heading in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_7</t>
   </si>
   <si>
@@ -227,6 +254,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_7 already clicks the link and checks the page is launched (active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Cambridge One for schools page opens in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_4</t>
   </si>
   <si>
@@ -245,6 +275,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Source row split one case per link. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_4 already is registered but COMMENTED OUT in footer.test.js — re-enable it and make it assert the new tab (ADR-016 tab helpers). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Our approach link opens Cambridge English site in new tab and refocuses.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_6</t>
   </si>
   <si>
@@ -260,6 +293,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_6 already is registered but COMMENTED OUT in footer.test.js — re-enable it and make it assert the new tab. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: FAQs opens help centre in a new tab and refocuses.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_8</t>
   </si>
   <si>
@@ -270,6 +306,59 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_8 already is registered but COMMENTED OUT in footer.test.js — re-enable it and make it assert the new tab. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: Help opens help centre in a new tab and refocuses.</t>
+  </si>
+  <si>
+    <t>TST_LAND_TC_8</t>
+  </si>
+  <si>
+    <t>Verify primary login page - {url}/login-primary</t>
+  </si>
+  <si>
+    <t>TC_HOME_007 — Verify primary login page - {url}/login-primary</t>
+  </si>
+  <si>
+    <t>1. Go to the pre-login homepage / navigate to {url}/login-primary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The header shows the Cambridge One logo/home link.
+2. The page shows the Primary-themed background image and the 'Welcome to Cambridge One' heading.
+3. The login area shows the username/email field, the password field, a 'Log in' button and a 'Forgot password' link.
+4. Entering valid credentials and clicking 'Log in' takes the user to their dashboard, while invalid or empty credentials show an error message.
+5. The footer shows 'Terms of use', 'Privacy notice', 'Accessibility', 'Our approach', 'FAQs', 'Cambridge One for schools', the copyright line '© Cambridge University Press &amp; Assessment 2026', and 'Help'.</t>
+  </si>
+  <si>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Direct entry to the primary-themed login route.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
+    <t>TST_LAND_TC_9</t>
+  </si>
+  <si>
+    <t>Verify secondary login page - {url}/login-secondary</t>
+  </si>
+  <si>
+    <t>TC_HOME_008 — Verify secondary login page - {url}/login-secondary</t>
+  </si>
+  <si>
+    <t>1. Go to the pre-login homepage / navigate to {url}/login-secondary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The header shows the Cambridge One logo/home link.
+2. The page shows the Secondary-themed background image and the 'Welcome to Cambridge One' heading.
+3. The login area shows the username/email field, the password field, a 'Log in' button and a 'Forgot password' link.
+4. Entering valid credentials and clicking 'Log in' takes the user to their dashboard, while invalid or empty credentials show an error message.
+5. The footer shows 'Terms of use', 'Privacy notice', 'Accessibility', 'Our approach', 'FAQs', 'Cambridge One for schools', the copyright line '© Cambridge University Press &amp; Assessment 2026', and 'Help'.</t>
+  </si>
+  <si>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Direct entry to the secondary-themed login route.</t>
   </si>
   <si>
     <t>TST_LOGI_TC_5</t>
@@ -325,6 +414,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Side-effect free.</t>
   </si>
   <si>
+    <t>Verified on Production: required-field validation messages displayed for username and password fields on blank submit.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 2)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_8</t>
   </si>
   <si>
@@ -361,7 +456,7 @@
     <t>TC_LOGIN_004 — Verify the account is temporarily locked after 5 consecutive failed login attempts</t>
   </si>
   <si>
-    <t>A registered, DISPOSABLE test account exists (not used by any other case). User is on the Log in page (homepage → "Log in").</t>
+    <t>A dedicated test account (cqatestuserforblockDND@mailsac.com) exists for lockout testing. User is on the Log in page (homepage → "Log in").</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter the account's e-mail with an incorrect password and click 'Log in'.
@@ -369,14 +464,14 @@
 3. Try a 6th time with the CORRECT password.</t>
   </si>
   <si>
-    <t>&lt;DISPOSABLE_ACCOUNT_EMAIL&gt;; wrong password ×5, then the correct password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>cqatestuserforblockDND@mailsac.com; wrong password ×5, then the correct password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Each of the first 5 attempts shows the 'check your login and password' alert referencing the 5-attempt limit.
-2. After the 5th failure the account is temporarily locked: the 6th attempt, even with the correct password, is rejected.</t>
-  </si>
-  <si>
-    <t>Source: OnboardingApp_Test_Plan.xlsx. LOCKS AN ACCOUNT — never a shared/pool account (migration plan Q10). Needs a disposable account per run (e.g. one created by the signup suite). Lockout duration and the exact 5th/6th-attempt copy are [ASSUMED] — not stated in the source.</t>
+2. After the 5th failure the account is temporarily locked for 2 minutes: the 6th attempt, even with the correct password, is rejected.</t>
+  </si>
+  <si>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Account is locked for 2 minutes on 5 consecutive wrong password attempts (user confirmed 2026-09-24). Uses dedicated test user cqatestuserforblockDND@mailsac.com.</t>
   </si>
   <si>
     <t>TST_LOGI_TC_10</t>
@@ -403,6 +498,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. The existing TST_LOGI_TC_3 (login.test.js, not registered in C1TCRepository) only clicks the eye icon; this case asserts the field type. Automation reuses the click.</t>
   </si>
   <si>
+    <t>Verified on Production: password field type changes from password to text and back to password on clicking show password toggle.</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_4</t>
   </si>
   <si>
@@ -419,6 +517,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LOGI_TC_4 already clicks Forgotten your password and checks the reset page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: Forgotten your password link navigates to the reset password form.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 3)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_6</t>
@@ -664,6 +768,12 @@
     <t xml:space="preserve">Source: OnboardingApp_Test_Plan.xlsx. </t>
   </si>
   <si>
+    <t>Verified on Production: submitting blank email displays 'This field is required' error message.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 3 via TST_RESE_TC_2)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_7</t>
   </si>
   <si>
@@ -724,6 +834,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_RESE_TC_4 already clicks Back to login and checks the login page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Back to login navigates back to the Login form.</t>
   </si>
   <si>
     <t>TST_RESE_TC_9</t>
@@ -880,6 +993,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. onboarding.md §A1: Next is natively disabled until a role is picked (seen live, thor 2026-09-22).</t>
   </si>
   <si>
+    <t>Verified on Production: Learner, Teacher, and Parent role options are displayed with none pre-selected and Next button disabled.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 4)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_66</t>
   </si>
   <si>
@@ -905,6 +1024,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. The existing TST_SNUP_TC_59 checks the dialog NAMES the role and then continues; this case asserts the full copy and both buttons and stops at the dialog.</t>
   </si>
   <si>
+    <t>Verified on Production: modal dialog confirms selected role ('You have selected Teacher. Please check this is the right role') with 'Yes, continue' and 'No, go back' buttons.</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_67</t>
   </si>
   <si>
@@ -921,6 +1043,9 @@
     <t>The dialog closes, the user stays on the role-selection page and 'Teacher' is still selected.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking 'No, go back' closes dialog and retains previously selected role.</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_59</t>
   </si>
   <si>
@@ -943,6 +1068,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_SNUP_TC_59 already selects a role, checks the dialog names it, clicks Yes, continue and checks the role's next screen (data: role, expectedScreen) — run it for Parent too. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking 'Yes, continue' on confirmation dialog navigates to the role registration flow (Learner age gate).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 5 via TST_SNUP_TC_69)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_68</t>
   </si>
   <si>
@@ -956,6 +1087,9 @@
   </si>
   <si>
     <t>The Log in form is shown.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Login link on role selection page navigates to Login form.</t>
   </si>
   <si>
     <t>TST_SNUP_TC_69</t>
@@ -975,6 +1109,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. URL /learner-age-check (onboarding.md §A2). ⚠️ On thor the first-name box also reported visible on this screen (onboarding.md §A2) — check.</t>
+  </si>
+  <si>
+    <t>Verified on Production: learner age check screen (/learner-age-check) is displayed with Location field and Your age dropdown.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 5)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_70</t>
@@ -1004,6 +1144,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Legend 'Learner age gate': India blocks 13–15 (source: confirmed live). Side-effect free.</t>
   </si>
   <si>
+    <t>Verified on Production: selecting underage (13-15) for India displays 'We\'re sorry' blocked screen and 'Go back' button.</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_71</t>
   </si>
   <si>
@@ -1028,6 +1171,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Legend 'Learner age gate': threshold is location-dependent — India blocks 13–15 / allows 16+; United Kingdom blocks 11–12 / allows 13+ (source: confirmed live). Boundary pairs worth adding in Phase 1: India 15/16, UK 12/13.</t>
+  </si>
+  <si>
+    <t>Verified on Production: age dropdown presents options (18+, 17 down to 5); age options verified on learner age check screen.</t>
   </si>
   <si>
     <t>TST_SNUP_TC_63</t>
@@ -1051,6 +1197,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_SNUP_TC_63 already sets country + age and checks the learner profile form opens (LP setup chain). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: selecting age 16+ (18+) with Location India allows user to proceed to the Learner registration profile form.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 5 via TST_SNUP_TC_76 prerequisite)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_72</t>
@@ -1107,6 +1259,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Side-effect free (never submits a valid form).</t>
+  </si>
+  <si>
+    <t>Verified on Production: required-field errors ('This field is required') displayed for First name and Last name on blank form submission.</t>
   </si>
   <si>
     <t>TST_SNUP_TC_73</t>
@@ -1510,12 +1665,15 @@
   <si>
     <t>Role: 'Parent' (source); data-driven for Teacher / Learner</t>
   </si>
+  <si>
+    <t>Verified on Production: clicking Login link on Learner registration form returns user to Login page (/login).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1527,8 +1685,12 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF155724"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1538,6 +1700,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3D1A66"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1563,7 +1730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1571,10 +1738,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1916,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2017,14 +2187,14 @@
       <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -2032,46 +2202,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2079,46 +2249,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2126,13 +2296,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -2141,31 +2311,31 @@
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2173,13 +2343,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -2191,28 +2361,28 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -2220,13 +2390,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
@@ -2238,28 +2408,28 @@
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -2267,13 +2437,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
@@ -2285,28 +2455,28 @@
         <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2314,13 +2484,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -2332,28 +2502,28 @@
         <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -2361,13 +2531,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
@@ -2379,28 +2549,28 @@
         <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2408,13 +2578,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
@@ -2426,28 +2596,28 @@
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2455,13 +2625,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>18</v>
@@ -2473,28 +2643,28 @@
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2502,46 +2672,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2549,46 +2719,46 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2596,46 +2766,46 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="N15" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2643,46 +2813,46 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -2690,46 +2860,46 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -2737,46 +2907,46 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -2784,13 +2954,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
@@ -2799,45 +2969,45 @@
         <v>19</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>136</v>
+      <c r="B20" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>18</v>
@@ -2846,45 +3016,45 @@
         <v>19</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>144</v>
+        <v>161</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>145</v>
+      <c r="B21" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>18</v>
@@ -2893,125 +3063,125 @@
         <v>19</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>144</v>
+        <v>104</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>152</v>
+      <c r="B22" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>144</v>
+        <v>104</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>160</v>
+      <c r="B23" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>27</v>
+        <v>104</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3019,43 +3189,43 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>176</v>
@@ -3065,61 +3235,61 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>177</v>
+      <c r="B25" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>91</v>
+        <v>198</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>184</v>
+      <c r="B26" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
@@ -3128,45 +3298,45 @@
         <v>19</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>190</v>
+      <c r="B27" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>18</v>
@@ -3175,78 +3345,78 @@
         <v>19</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>195</v>
+        <v>118</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>27</v>
+        <v>104</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>197</v>
+      <c r="B28" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>27</v>
+        <v>104</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3254,46 +3424,46 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>208</v>
+        <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3301,46 +3471,46 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>25</v>
+        <v>237</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3348,46 +3518,46 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3395,46 +3565,46 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>91</v>
+        <v>250</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -3442,13 +3612,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>18</v>
@@ -3457,31 +3627,31 @@
         <v>19</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>236</v>
+        <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>25</v>
+        <v>161</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -3489,46 +3659,46 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -3536,46 +3706,46 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3583,46 +3753,46 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -3630,46 +3800,46 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>20</v>
+        <v>284</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -3677,46 +3847,46 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -3724,46 +3894,46 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>203</v>
+        <v>302</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>25</v>
+        <v>304</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -3771,46 +3941,46 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>25</v>
+        <v>304</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -3818,13 +3988,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>18</v>
@@ -3833,31 +4003,31 @@
         <v>19</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>22</v>
+        <v>310</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>25</v>
+        <v>304</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -3865,46 +4035,46 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>22</v>
+        <v>324</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>25</v>
+        <v>328</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -3912,46 +4082,46 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="I43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="O43" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -3959,46 +4129,46 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="H44" s="2" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>312</v>
+        <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -4006,46 +4176,46 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -4053,46 +4223,46 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>18</v>
+        <v>355</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -4100,46 +4270,46 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>25</v>
+        <v>369</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -4147,46 +4317,46 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>271</v>
+        <v>373</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -4194,46 +4364,46 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>345</v>
+        <v>379</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -4241,46 +4411,46 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>354</v>
+        <v>388</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>356</v>
+        <v>390</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>358</v>
+        <v>392</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -4288,46 +4458,46 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>359</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>361</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>363</v>
+        <v>397</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -4335,46 +4505,46 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>370</v>
+        <v>308</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -4382,46 +4552,46 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -4429,46 +4599,46 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>382</v>
+        <v>416</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>383</v>
+        <v>417</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>384</v>
+        <v>418</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -4476,46 +4646,46 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4523,107 +4693,107 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>399</v>
+        <v>432</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>401</v>
+        <v>434</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>402</v>
+        <v>435</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>406</v>
+      <c r="B57" s="2" t="s">
+        <v>439</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>22</v>
+        <v>444</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>183</v>
+        <v>446</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>411</v>
+      <c r="B58" s="2" t="s">
+        <v>447</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>413</v>
+        <v>449</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>18</v>
@@ -4632,45 +4802,45 @@
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>271</v>
+        <v>450</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>22</v>
+        <v>452</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>415</v>
+        <v>453</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>183</v>
+        <v>454</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O58" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>416</v>
+      <c r="B59" s="5" t="s">
+        <v>455</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>417</v>
+        <v>456</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>418</v>
+        <v>457</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>18</v>
@@ -4679,45 +4849,45 @@
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>420</v>
+        <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O59" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>422</v>
+      <c r="B60" s="5" t="s">
+        <v>460</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>18</v>
@@ -4726,45 +4896,45 @@
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>271</v>
+        <v>308</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>426</v>
+        <v>464</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O60" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>427</v>
+      <c r="B61" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>18</v>
@@ -4773,45 +4943,45 @@
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>430</v>
+        <v>308</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O61" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>434</v>
+      <c r="B62" s="5" t="s">
+        <v>471</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>18</v>
@@ -4820,45 +4990,45 @@
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>437</v>
+        <v>308</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>439</v>
+        <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>440</v>
+        <v>475</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O62" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>441</v>
+      <c r="B63" s="5" t="s">
+        <v>476</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>18</v>
@@ -4867,45 +5037,45 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>445</v>
+        <v>480</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>447</v>
+        <v>482</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O63" s="4" t="s">
-        <v>176</v>
+        <v>104</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>448</v>
+      <c r="B64" s="5" t="s">
+        <v>483</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>450</v>
+        <v>485</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>18</v>
@@ -4914,39 +5084,133 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>451</v>
+        <v>486</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>291</v>
+        <v>487</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>292</v>
+        <v>489</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="M64" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>27</v>
+      <c r="N66" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="M10:M64">
+    <dataValidation type="list" allowBlank="1" sqref="M10:M66">
       <formula1>"Not Run,Pass,Fail,Blocked,On Hold"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M2:M64">
+    <dataValidation type="list" allowBlank="1" sqref="M2:M66">
       <formula1>"Not Run,Pass,Fail,Blocked,On Hold"</formula1>
     </dataValidation>
   </dataValidations>

--- a/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
@@ -289,7 +289,7 @@
 3. Click 'Log in'.</t>
   </si>
   <si>
-    <t>&lt;REGISTERED_ACCOUNT_EMAIL&gt; + its password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>&lt;REGISTERED_ACCOUNT_EMAIL&gt; + its password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t>The user is logged in and lands on their role's dashboard.</t>
@@ -369,7 +369,7 @@
 3. Try a 6th time with the CORRECT password.</t>
   </si>
   <si>
-    <t>&lt;DISPOSABLE_ACCOUNT_EMAIL&gt;; wrong password ×5, then the correct password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>&lt;DISPOSABLE_ACCOUNT_EMAIL&gt;; wrong password ×5, then the correct password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Each of the first 5 attempts shows the 'check your login and password' alert referencing the 5-attempt limit.
@@ -531,7 +531,7 @@
 3. Click 'Log in'.</t>
   </si>
   <si>
-    <t>&lt;SCHOOL_ADMIN_EMAIL&gt; + its password (the admin suites' existing admin login). Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>&lt;SCHOOL_ADMIN_EMAIL&gt; + its password (the admin suites' existing admin login). Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. The Admin is logged in through the same form as every other role.
@@ -746,7 +746,7 @@
 6. Log in with the e-mail and the NEW password.</t>
   </si>
   <si>
-    <t>&lt;MAILSAC_ACCOUNT_EMAIL&gt;; a new password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>&lt;MAILSAC_ACCOUNT_EMAIL&gt;; a new password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. CHANGES A REAL ACCOUNT'S PASSWORD — use a disposable account (e.g. one created by the signup suite in the same run), never a shared fixture. Mail handling as mailsacUI.openVerificationLink (sandboxed mail iframe, follow the link on the same page — c1-core-shared.md §A5/§B3). The reset link host may be the same login.comprodls.com host whose thor certificate is expired [ASSUMED — check].</t>
@@ -796,7 +796,7 @@
 3. Enter a temporary password and submit.</t>
   </si>
   <si>
-    <t>A temporary password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>A temporary password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. The student's options menu offers 'View profile', 'Activate course material' and 'Change password'.
@@ -822,7 +822,7 @@
 4. Log out and log in again with the new password.</t>
   </si>
   <si>
-    <t>The temporary password; a different new password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>The temporary password; a different new password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. The login does not go straight to the dashboard — a temporary-password screen asks for the temporary password, a new password and its confirmation.
@@ -851,7 +851,7 @@
 4. Enter a temporary password and submit.</t>
   </si>
   <si>
-    <t>A disposable student; a temporary password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>A disposable student; a temporary password meeting the complexity rules. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. The Action Menu offers a way to change the student's password (alongside 'View profile' and 'Activate course materials').
@@ -1072,7 +1072,7 @@
 5. Verify the account from the Mailsac e-mail.</t>
   </si>
   <si>
-    <t>Unique &lt;RUN_LEARNER_EMAIL&gt;@mailsac.com ({{run.*}} token, ADR-022); a complexity-compliant password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>Unique &lt;RUN_LEARNER_EMAIL&gt;@mailsac.com ({{run.*}} token, ADR-022); a complexity-compliant password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Location is pre-filled from the age/location screen and cannot be edited.
@@ -1126,7 +1126,7 @@
 6. Verify the account from the Mailsac e-mail.</t>
   </si>
   <si>
-    <t>Unique &lt;RUN_TEACHER_EMAIL&gt;@mailsac.com ({{run.*}}); Location 'India'. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>Unique &lt;RUN_TEACHER_EMAIL&gt;@mailsac.com ({{run.*}}); Location 'India'. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. The Teacher form comes straight after role confirmation, with no age gate: First name, Last name, Work email, Password, Location.
@@ -1185,7 +1185,7 @@
 7. Verify the account from the Mailsac e-mail.</t>
   </si>
   <si>
-    <t>Unique &lt;RUN_PARENT_EMAIL&gt;@mailsac.com ({{run.*}}); Location 'India'. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>Unique &lt;RUN_PARENT_EMAIL&gt;@mailsac.com ({{run.*}}); Location 'India'. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. The Parent form comes straight after role confirmation, with no age gate, and has an extra checkbox not on the Learner/Teacher forms: 'I am 18 years of age or older and I am the parent or guardian of any child whose account I set up'.
@@ -1241,7 +1241,7 @@
 6. Click 'Create account'.</t>
   </si>
   <si>
-    <t>Child first/last name, month and year of birth; child username + password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>Child first/last name, month and year of birth; child username + password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. 'Add child' opens 'Create my child's account' in an embedded panel with first name, last name, month of birth, year of birth and one checkbox 'I accept the Privacy notice and Terms of use on behalf of my child' ('Privacy notice' and 'Terms of use' are separate links).
@@ -1321,7 +1321,7 @@
 6. Click 'Sign up'.</t>
   </si>
   <si>
-    <t>A fresh &lt;RUN_INVITEE_EMAIL&gt;@mailsac.com ({{run.*}}). Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>A fresh &lt;RUN_INVITEE_EMAIL&gt;@mailsac.com ({{run.*}}). Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-025).</t>
   </si>
   <si>
     <t xml:space="preserve">1. 'View invite' opens the Learner sign-up form directly (no role selection) with School email pre-filled and disabled to the invited address.

--- a/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="520">
   <si>
     <t>S.No.</t>
   </si>
@@ -333,10 +333,10 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Direct entry to the primary-themed login route.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
+    <t>Verified on Production: /login-primary loads with brand logo, primary header, submit button, and footer links.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 2)</t>
   </si>
   <si>
     <t>TST_LAND_TC_9</t>
@@ -361,6 +361,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Direct entry to the secondary-themed login route.</t>
   </si>
   <si>
+    <t>Verified on Production: /login-secondary loads with brand logo, secondary header, submit button, and footer links.</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_5</t>
   </si>
   <si>
@@ -387,6 +390,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LOGI_TC_5 already clicks Log in and checks the dashboard loads (composed after LOGI_TC_1/2, which type the credentials). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: user logs in with valid student credentials and lands on dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 3 via TST_LOGI_TC_1/2/5)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_7</t>
   </si>
   <si>
@@ -447,6 +456,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Counts as 1 of the 5 attempts before lockout (see TST_LOGI_TC_9) — never run it repeatedly on a shared account; use a disposable one or one whose counter resets on success.</t>
   </si>
   <si>
+    <t>Verified on Production: generic credentials error alert displayed on invalid password and user remains on /login.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 3)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_9</t>
   </si>
   <si>
@@ -474,6 +489,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Account is locked for 2 minutes on 5 consecutive wrong password attempts (user confirmed 2026-09-24). Uses dedicated test user cqatestuserforblockDND@mailsac.com.</t>
   </si>
   <si>
+    <t>Verified on Production: 5 consecutive failed login attempts show 5-attempt limit warning, and 6th attempt with valid password is rejected with account temporarily locked message.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 4)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_10</t>
   </si>
   <si>
@@ -543,6 +564,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LOGI_TC_6 already clicks Sign up on the login form and checks the page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking 'Don\'t have an account yet?' navigates to role selection screen (/regoptions).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 1 via TST_LOGI_TC_6)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_11</t>
   </si>
   <si>
@@ -569,6 +596,12 @@
     <t xml:space="preserve">NOT FOR AUTOMATION — marked YELLOW in the source plan (user, 2026-09-24): needs bulk-created username accounts; the first-login gate appears once per account. Manual execution only. Source: OnboardingApp_Test_Plan.xlsx. </t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Manual only — YELLOW in source (not for automation)</t>
   </si>
   <si>
@@ -643,6 +676,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Every admin suite already logs in this way (login.click_login_btn_schoolAdmin in their Before) but none asserts it as a case.</t>
+  </si>
+  <si>
+    <t>Verified on Production: school admin logs in through standard form and reaches /admin/admin/ dashboard.</t>
   </si>
   <si>
     <t>TST_LOGI_TC_15</t>
@@ -745,6 +781,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_APPS_TC_2 already clicks Log out (after TST_APPS_TC_1 opens the menu) and checks the landing page. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not. Knowledge: SOURCE saw logout land on /home OR /login?rurl=… — both are logged-out states; confirm which one the learner gets.</t>
   </si>
   <si>
+    <t>Verified on Production: logging out redirects to landing page with Log in and Sign up options.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 3 via TST_APPS_TC_1/2)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_6</t>
   </si>
   <si>
@@ -796,6 +838,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. SENDS A REAL RESET E-MAIL to the account (harmless: the password only changes if the link is used). Use a Mailsac-inbox account, not a shared login.</t>
   </si>
   <si>
+    <t>Verified on Production: reset password confirmation screen displays heading "Reset password email sent" and informational body text for registered email.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 1)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_8</t>
   </si>
   <si>
@@ -816,6 +864,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Legend 'Generic reset message': identical by design (no account enumeration), not a bug. 'No reset e-mail is actually sent' can only be checked in the Mailsac inbox.</t>
+  </si>
+  <si>
+    <t>Verified on Production: reset password confirmation screen displays identical generic heading "Reset password email sent" and informational body text for unregistered email (no account enumeration).</t>
   </si>
   <si>
     <t>TST_RESE_TC_4</t>
@@ -2704,11 +2755,11 @@
       <c r="L13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -2749,13 +2800,13 @@
         <v>111</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2766,13 +2817,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>18</v>
@@ -2781,28 +2832,28 @@
         <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>105</v>
+        <v>121</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>28</v>
@@ -2813,43 +2864,43 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>28</v>
@@ -2860,43 +2911,43 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>105</v>
+        <v>141</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2907,43 +2958,43 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>105</v>
+        <v>151</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>28</v>
@@ -2954,13 +3005,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
@@ -2969,28 +3020,28 @@
         <v>19</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -3001,13 +3052,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>18</v>
@@ -3016,28 +3067,28 @@
         <v>19</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -3048,13 +3099,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>18</v>
@@ -3063,28 +3114,28 @@
         <v>19</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>105</v>
+        <v>175</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>28</v>
@@ -3095,13 +3146,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>18</v>
@@ -3110,31 +3161,31 @@
         <v>19</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3142,13 +3193,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
@@ -3157,31 +3208,31 @@
         <v>19</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3189,46 +3240,46 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="O24" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3236,13 +3287,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>18</v>
@@ -3251,28 +3302,28 @@
         <v>32</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>105</v>
+        <v>211</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -3283,13 +3334,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
@@ -3298,31 +3349,31 @@
         <v>19</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3330,13 +3381,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>18</v>
@@ -3345,31 +3396,31 @@
         <v>19</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3377,13 +3428,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>18</v>
@@ -3392,31 +3443,31 @@
         <v>19</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="O28" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="O28" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3424,13 +3475,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>18</v>
@@ -3439,28 +3490,28 @@
         <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>105</v>
+        <v>241</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>104</v>
+        <v>242</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -3471,43 +3522,43 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -3518,13 +3569,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>18</v>
@@ -3533,28 +3584,28 @@
         <v>32</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>105</v>
+        <v>259</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -3565,43 +3616,43 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>105</v>
+        <v>268</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>104</v>
+        <v>260</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -3612,13 +3663,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>18</v>
@@ -3627,28 +3678,28 @@
         <v>19</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -3659,13 +3710,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>18</v>
@@ -3674,28 +3725,28 @@
         <v>32</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -3706,13 +3757,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>18</v>
@@ -3721,28 +3772,28 @@
         <v>19</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -3753,13 +3804,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>18</v>
@@ -3768,28 +3819,28 @@
         <v>32</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -3800,13 +3851,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>18</v>
@@ -3815,28 +3866,28 @@
         <v>32</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>28</v>
@@ -3847,13 +3898,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>18</v>
@@ -3862,28 +3913,28 @@
         <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -3894,13 +3945,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>18</v>
@@ -3912,25 +3963,25 @@
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -3941,13 +3992,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>18</v>
@@ -3956,28 +4007,28 @@
         <v>32</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -3988,13 +4039,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>18</v>
@@ -4003,28 +4054,28 @@
         <v>19</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -4035,13 +4086,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>18</v>
@@ -4050,28 +4101,28 @@
         <v>32</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -4082,13 +4133,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>18</v>
@@ -4097,28 +4148,28 @@
         <v>19</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -4129,13 +4180,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>18</v>
@@ -4144,28 +4195,28 @@
         <v>32</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -4176,43 +4227,43 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -4223,43 +4274,43 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -4270,13 +4321,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>18</v>
@@ -4285,28 +4336,28 @@
         <v>19</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -4317,13 +4368,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>18</v>
@@ -4332,28 +4383,28 @@
         <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -4364,43 +4415,43 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -4411,13 +4462,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>18</v>
@@ -4426,28 +4477,28 @@
         <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -4458,43 +4509,43 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -4505,13 +4556,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>18</v>
@@ -4520,28 +4571,28 @@
         <v>32</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -4552,43 +4603,43 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -4599,13 +4650,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>18</v>
@@ -4614,28 +4665,28 @@
         <v>32</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -4646,43 +4697,43 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -4693,13 +4744,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>18</v>
@@ -4708,28 +4759,28 @@
         <v>32</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -4740,13 +4791,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>18</v>
@@ -4755,28 +4806,28 @@
         <v>32</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -4787,13 +4838,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>18</v>
@@ -4802,28 +4853,28 @@
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -4834,13 +4885,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>18</v>
@@ -4852,28 +4903,28 @@
         <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -4881,13 +4932,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>18</v>
@@ -4896,31 +4947,31 @@
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -4928,13 +4979,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>18</v>
@@ -4943,31 +4994,31 @@
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -4975,13 +5026,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>18</v>
@@ -4990,31 +5041,31 @@
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -5022,13 +5073,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>18</v>
@@ -5037,31 +5088,31 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -5069,13 +5120,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>18</v>
@@ -5084,31 +5135,31 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O64" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -5116,13 +5167,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>18</v>
@@ -5131,31 +5182,31 @@
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="O65" s="5" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -5163,13 +5214,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>18</v>
@@ -5178,28 +5229,28 @@
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>

--- a/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="544">
   <si>
     <t>S.No.</t>
   </si>
@@ -916,6 +916,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CHANGES A REAL ACCOUNT'S PASSWORD — use a disposable account (e.g. one created by the signup suite in the same run), never a shared fixture. Mail handling as mailsacUI.openVerificationLink (sandboxed mail iframe, follow the link on the same page — c1-core-shared.md §A5/§B3). The reset link host may be the same login.comprodls.com host whose thor certificate is expired [ASSUMED — check].</t>
   </si>
   <si>
+    <t>Verified on Production: password reset requested, link extracted from Mailsac inbox, new password saved and confirmed via modal dialog, and user successfully logs in with new password.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 5)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_10</t>
   </si>
   <si>
@@ -943,6 +949,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. OVERLAP: the source's TC_FPWD_005 already ends with this login (its steps 5–6). Kept as its own row because the source has it; see Open items — the automation may compose LOGI_TC_1/2/5 with the new password instead of a new function.</t>
   </si>
   <si>
+    <t>Verified on Production: user logs out from active session, enters credentials with newly reset password on /login, and reaches role dashboard.</t>
+  </si>
+  <si>
     <t>TST_CREA_TC_31</t>
   </si>
   <si>
@@ -969,6 +978,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. First half of the source row; the student's first login with the temporary password is TST_LOGI_TC_18. CHANGES A REAL STUDENT'S PASSWORD — disposable student only. Module CREA = the teacher class page object (createNewClass.page.js); if Phase 1 finds the roster lives on another page object, re-code before automating. Confirmation copy after submit is [ASSUMED] (not in the source).</t>
+  </si>
+  <si>
+    <t>Verified on Production: Teacher opens class roster on Class data tab, locates student Actions menu, and verifies options to change password and manage student.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 8 via TST_CREA_TC_31)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_18</t>
@@ -994,7 +1009,7 @@
 3. The student can log in again with the new, self-set password.</t>
   </si>
   <si>
-    <t>Source: OnboardingApp_Test_Plan.xlsx. Serves BOTH TC_RESETPW_001 and TC_RESETPW_002 (same screen, different staff entry). Legend 'Password reset caveat': the same Gigya temporary-password screen-set as an Admin resetting their own password.</t>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Serves BOTH TC_RESETPW_001 and TC_RESETPW_002 (same screen, different staff entry). Out of automation scope per user instruction.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_24</t>
@@ -1023,6 +1038,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. [ASSUMED] entry point — the source's Legend says it was "taken from existing documentation … not independently re-verified live". OVERLAP to settle in Phase 1: the Students register already has TST_SPRF_TC_8 (admin sets a NEW password via View profile &gt; Manage account &gt; Password tab) and TST_SPRF_TC_23 (learner signs in with it). This row differs by the row Action Menu entry and the TEMPORARY-password first-login screen — confirm live that these are two different flows before automating. CHANGES A REAL STUDENT'S PASSWORD — disposable student only.</t>
+  </si>
+  <si>
+    <t>Verified on Production: School admin navigates to Learners tab, accesses learner profile, opens Manage learner profile, sets temporary password, and submits update.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 8 via TST_SPRF_TC_24)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_65</t>
@@ -1283,6 +1304,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Thor: the e-mail verification link host has an EXPIRED certificate (c1-core-shared.md §A4) — the verify step is blocked on thor until renewed; production works. New assertion = the locked, pre-filled Location. Account creation/verification reuse existing TST_SNUP_TC_60 (submit → pending screen), TST_SNUP_TC_61 (Mailsac link), TST_SNUP_TC_64 (learner welcome).</t>
+  </si>
+  <si>
+    <t>Verified on Production: Location is locked to pre-filled value from age check, user completes registration form, verifies account via Mailsac link, and successfully accesses Learner dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 2)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_76</t>
@@ -1342,6 +1369,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Thor: the e-mail verification link host has an EXPIRED certificate (c1-core-shared.md §A4) — the verify step is blocked on thor until renewed; production works. New assertion = the Teacher form's fields / no age gate. Creation and verification reuse existing TST_SNUP_TC_60, TST_SNUP_TC_61, TST_SNUP_TC_62 (tour + "Complete account set up").</t>
   </si>
   <si>
+    <t>Verified on Production: Teacher registration form opens directly with no age gate, user completes registration, verifies account via Mailsac link, and reaches Teacher dashboard / complete account setup prompt.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 3)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_77</t>
   </si>
   <si>
@@ -1371,6 +1404,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Side-effect free. Terms checkbox id differs by env (thor #legal-checkbox-1, prod #teacher-checkbox-1 — onboarding.md §A3).</t>
+  </si>
+  <si>
+    <t>Verified on Production: required-field errors ('This field is required') shown for First name, Last name, Location; 'E-mail address is invalid.' for Work email; 'Password does not meet complexity requirements' for weak password; Terms alert displayed when unchecked.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 1)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_74</t>
@@ -1401,6 +1440,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Thor: the e-mail verification link host has an EXPIRED certificate (c1-core-shared.md §A4) — the verify step is blocked on thor until renewed; production works. Resolves onboarding.md §A2's [ASSUMED] Parent row. Creation/verification reuse TST_SNUP_TC_60/61; the parent dashboard assertion is new.</t>
   </si>
   <si>
+    <t>Verified on Production: Parent registration form includes age 18+ / guardian consent checkbox, user completes registration, verifies account via Mailsac link, and reaches Parent dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 4)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_75</t>
   </si>
   <si>
@@ -1425,6 +1470,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Any message shown for the missing checkbox is not stated in the source — capture it verbatim in Phase 1 [ASSUMED]. Side-effect free if the form really does not submit; use a {{run.*}} e-mail anyway in case it does.</t>
+  </si>
+  <si>
+    <t>Verified on Production: Parent form does not submit without guardian consent, user remains on /register-parent, and parental checkbox highlights with error state (.parent-error).</t>
   </si>
   <si>
     <t>TST_PCHD_TC_1</t>
@@ -1458,6 +1506,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. PROPOSED module PCHD — no parent/child page object exists yet (migration plan U20, K19: the child form sits in a Gigya #child-iframe). CREATES A CHILD ACCOUNT. SOURCE reported child creation FAILING ON THOR [2026] — Phase 1 must check; if still failing, mark Blocked there (unblock: product fix or run on another env with the user's OK).</t>
   </si>
   <si>
+    <t>Verified on Production: Parent creates child account from 'My children', completes embedded panel details with consent checkbox, enters child username &amp; password, and receives account created confirmation with username.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 6)</t>
+  </si>
+  <si>
     <t>TST_PCHD_TC_2</t>
   </si>
   <si>
@@ -1478,6 +1532,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Exact inline error copy is not in the source — capture verbatim in Phase 1 [ASSUMED]. Side-effect free.</t>
+  </si>
+  <si>
+    <t>Verified on Production: on 'Create my child's account' blank submission displays required-field errors ('This field is required', 'This field is required (Month and Year)'), and form stays blocked on Subscreen 1 without ticking the consent checkbox.</t>
   </si>
   <si>
     <t>TST_PCHD_TC_3</t>
@@ -1505,6 +1562,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Depends on TST_PCHD_TC_1 in the same run.</t>
+  </si>
+  <si>
+    <t>Verified on Production: newly created child account logs in with username and password on /login, and successfully reaches the Learner dashboard ('Learner dashboard | Cambridge One').</t>
   </si>
   <si>
     <t>TST_INVI_TC_14</t>
@@ -1539,6 +1599,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Needs a teacher + class and an invite (reuse TST_CREA_TC_19–24 for the invite). Module INVI (invitation flow); if Phase 1 finds the invite signup form is the signup page object, re-code to SNUP before automating. Legend: invite signup has NO age gate.</t>
   </si>
   <si>
+    <t>Verified on Production: Teacher invites unregistered student, invitee opens 'View invite' link from Mailsac email, completes registration with prefilled email, verifies account via Mailsac, and reaches dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 7 via TST_INVI_TC_14)</t>
+  </si>
+  <si>
     <t>TST_INVI_TC_15</t>
   </si>
   <si>
@@ -1561,6 +1627,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Existing INVI_TC_1–6 cover accepting the invite from the in-app bell; this is the e-mail link path. Each run leaves a pending invite in the class (migration plan Q4).</t>
+  </si>
+  <si>
+    <t>Verified on Production: Teacher invites registered learner, learner opens 'View invite' link while logged in, and lands directly on their learner dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 7 via TST_INVI_TC_15)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_19</t>
@@ -3740,13 +3812,13 @@
         <v>282</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>186</v>
+        <v>283</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>185</v>
+        <v>284</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -3757,13 +3829,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>18</v>
@@ -3772,28 +3844,28 @@
         <v>19</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>186</v>
+        <v>293</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>185</v>
+        <v>284</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -3804,13 +3876,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>18</v>
@@ -3819,28 +3891,28 @@
         <v>32</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>186</v>
+        <v>302</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>185</v>
+        <v>303</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>28</v>
@@ -3850,14 +3922,14 @@
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>299</v>
+      <c r="B37" s="4" t="s">
+        <v>304</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>18</v>
@@ -3866,19 +3938,19 @@
         <v>32</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>185</v>
@@ -3889,8 +3961,8 @@
       <c r="N37" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="O37" s="2" t="s">
-        <v>28</v>
+      <c r="O37" s="4" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -3898,13 +3970,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>18</v>
@@ -3913,28 +3985,28 @@
         <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>186</v>
+        <v>319</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>185</v>
+        <v>320</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -3945,13 +4017,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>18</v>
@@ -3963,25 +4035,25 @@
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -3992,13 +4064,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>18</v>
@@ -4007,28 +4079,28 @@
         <v>32</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -4039,13 +4111,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>18</v>
@@ -4054,28 +4126,28 @@
         <v>19</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H41" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="J41" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>249</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -4086,13 +4158,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>18</v>
@@ -4101,28 +4173,28 @@
         <v>32</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -4133,13 +4205,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>18</v>
@@ -4148,28 +4220,28 @@
         <v>19</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>249</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -4180,13 +4252,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>18</v>
@@ -4195,28 +4267,28 @@
         <v>32</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -4227,13 +4299,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>126</v>
@@ -4242,28 +4314,28 @@
         <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -4274,43 +4346,43 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -4321,13 +4393,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>18</v>
@@ -4336,28 +4408,28 @@
         <v>19</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -4368,13 +4440,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>18</v>
@@ -4383,28 +4455,28 @@
         <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>186</v>
+        <v>402</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>185</v>
+        <v>403</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -4415,13 +4487,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>126</v>
@@ -4430,28 +4502,28 @@
         <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -4462,13 +4534,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>18</v>
@@ -4477,28 +4549,28 @@
         <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>186</v>
+        <v>419</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>185</v>
+        <v>420</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -4509,13 +4581,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>126</v>
@@ -4524,28 +4596,28 @@
         <v>32</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>186</v>
+        <v>429</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>185</v>
+        <v>430</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -4556,13 +4628,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>18</v>
@@ -4571,28 +4643,28 @@
         <v>32</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>186</v>
+        <v>438</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>185</v>
+        <v>439</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>28</v>
@@ -4603,13 +4675,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>126</v>
@@ -4618,28 +4690,28 @@
         <v>32</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="I53" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -4650,13 +4722,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>18</v>
@@ -4665,28 +4737,28 @@
         <v>32</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>186</v>
+        <v>457</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>185</v>
+        <v>458</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -4697,13 +4769,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>126</v>
@@ -4712,28 +4784,28 @@
         <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>186</v>
+        <v>466</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>185</v>
+        <v>458</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>28</v>
@@ -4744,13 +4816,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>18</v>
@@ -4759,28 +4831,28 @@
         <v>32</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>186</v>
+        <v>475</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>185</v>
+        <v>458</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -4791,13 +4863,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>18</v>
@@ -4806,28 +4878,28 @@
         <v>32</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>186</v>
+        <v>484</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>185</v>
+        <v>485</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -4838,13 +4910,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>18</v>
@@ -4853,28 +4925,28 @@
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>186</v>
+        <v>494</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>185</v>
+        <v>495</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -4885,13 +4957,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>18</v>
@@ -4903,13 +4975,13 @@
         <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>227</v>
@@ -4932,13 +5004,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>18</v>
@@ -4947,16 +5019,16 @@
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>227</v>
@@ -4979,13 +5051,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>18</v>
@@ -4994,16 +5066,16 @@
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>227</v>
@@ -5026,13 +5098,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>18</v>
@@ -5041,16 +5113,16 @@
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>227</v>
@@ -5073,13 +5145,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>18</v>
@@ -5088,16 +5160,16 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>497</v>
+        <v>521</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>227</v>
@@ -5120,13 +5192,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>18</v>
@@ -5135,16 +5207,16 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>227</v>
@@ -5167,13 +5239,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>18</v>
@@ -5182,16 +5254,16 @@
         <v>19</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>227</v>
@@ -5214,13 +5286,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>18</v>
@@ -5229,28 +5301,28 @@
         <v>19</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>249</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>28</v>

--- a/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/Onboarding/Onboarding_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="544">
   <si>
     <t>S.No.</t>
   </si>
@@ -90,10 +90,13 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Extends the existing TST_LAND_TC_5 (hero heading/sub-heading/buttons/logo) with the header and footer items — a new function, not a duplicate.</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
+    <t>Verified on Production: header logo/home link, language switcher, login/signup buttons, heading text, and all footer links are visible.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 1)</t>
   </si>
   <si>
     <t>Automate</t>
@@ -120,6 +123,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LAND_TC_3 already clicks Log in and checks the login page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking Log in navigates to the login page (/login).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 2, Suite 3)</t>
+  </si>
+  <si>
     <t>TST_LAND_TC_2</t>
   </si>
   <si>
@@ -136,6 +145,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LAND_TC_2 already clicks Sign up and checks the signup page is launched (used by the LP setup chain). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Sign up opens the role selection screen (/regoptions).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 4, Suite 5)</t>
   </si>
   <si>
     <t>TST_LAND_TC_7</t>
@@ -164,6 +179,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. The existing TST_LAND_TC_4 only opens the dropdown (asserts the click); this case asserts the outcome. Automation reuses LAND_TC_4 for the click.</t>
   </si>
   <si>
+    <t>Verified on Production: language switcher expands, changes language to Español, and reverts back to English.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_1</t>
   </si>
   <si>
@@ -182,6 +200,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Source row split one case per link. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_1 already clicks the link and checks the page is launched (footer.test.js, active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Terms of use page opens with expected heading in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_2</t>
   </si>
   <si>
@@ -197,6 +218,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_2 already clicks the link and checks the page is launched (active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Privacy notice page opens with expected heading in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_3</t>
   </si>
   <si>
@@ -212,6 +236,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_3 already clicks the link and checks the page is launched (active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Accessibility page opens with expected heading in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_7</t>
   </si>
   <si>
@@ -227,6 +254,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_7 already clicks the link and checks the page is launched (active). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Cambridge One for schools page opens in the same tab.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_4</t>
   </si>
   <si>
@@ -245,6 +275,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Source row split one case per link. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_4 already is registered but COMMENTED OUT in footer.test.js — re-enable it and make it assert the new tab (ADR-016 tab helpers). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Our approach link opens Cambridge English site in new tab and refocuses.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_6</t>
   </si>
   <si>
@@ -260,6 +293,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_6 already is registered but COMMENTED OUT in footer.test.js — re-enable it and make it assert the new tab. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: FAQs opens help centre in a new tab and refocuses.</t>
+  </si>
+  <si>
     <t>TST_FOOT_TC_8</t>
   </si>
   <si>
@@ -270,6 +306,62 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_FOOT_TC_8 already is registered but COMMENTED OUT in footer.test.js — re-enable it and make it assert the new tab. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: Help opens help centre in a new tab and refocuses.</t>
+  </si>
+  <si>
+    <t>TST_LAND_TC_8</t>
+  </si>
+  <si>
+    <t>Verify primary login page - {url}/login-primary</t>
+  </si>
+  <si>
+    <t>TC_HOME_007 — Verify primary login page - {url}/login-primary</t>
+  </si>
+  <si>
+    <t>1. Go to the pre-login homepage / navigate to {url}/login-primary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The header shows the Cambridge One logo/home link.
+2. The page shows the Primary-themed background image and the 'Welcome to Cambridge One' heading.
+3. The login area shows the username/email field, the password field, a 'Log in' button and a 'Forgot password' link.
+4. Entering valid credentials and clicking 'Log in' takes the user to their dashboard, while invalid or empty credentials show an error message.
+5. The footer shows 'Terms of use', 'Privacy notice', 'Accessibility', 'Our approach', 'FAQs', 'Cambridge One for schools', the copyright line '© Cambridge University Press &amp; Assessment 2026', and 'Help'.</t>
+  </si>
+  <si>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Direct entry to the primary-themed login route.</t>
+  </si>
+  <si>
+    <t>Verified on Production: /login-primary loads with brand logo, primary header, submit button, and footer links.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 2)</t>
+  </si>
+  <si>
+    <t>TST_LAND_TC_9</t>
+  </si>
+  <si>
+    <t>Verify secondary login page - {url}/login-secondary</t>
+  </si>
+  <si>
+    <t>TC_HOME_008 — Verify secondary login page - {url}/login-secondary</t>
+  </si>
+  <si>
+    <t>1. Go to the pre-login homepage / navigate to {url}/login-secondary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The header shows the Cambridge One logo/home link.
+2. The page shows the Secondary-themed background image and the 'Welcome to Cambridge One' heading.
+3. The login area shows the username/email field, the password field, a 'Log in' button and a 'Forgot password' link.
+4. Entering valid credentials and clicking 'Log in' takes the user to their dashboard, while invalid or empty credentials show an error message.
+5. The footer shows 'Terms of use', 'Privacy notice', 'Accessibility', 'Our approach', 'FAQs', 'Cambridge One for schools', the copyright line '© Cambridge University Press &amp; Assessment 2026', and 'Help'.</t>
+  </si>
+  <si>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Direct entry to the secondary-themed login route.</t>
+  </si>
+  <si>
+    <t>Verified on Production: /login-secondary loads with brand logo, secondary header, submit button, and footer links.</t>
   </si>
   <si>
     <t>TST_LOGI_TC_5</t>
@@ -298,6 +390,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LOGI_TC_5 already clicks Log in and checks the dashboard loads (composed after LOGI_TC_1/2, which type the credentials). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: user logs in with valid student credentials and lands on dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 3 via TST_LOGI_TC_1/2/5)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_7</t>
   </si>
   <si>
@@ -325,6 +423,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Side-effect free.</t>
   </si>
   <si>
+    <t>Verified on Production: required-field validation messages displayed for username and password fields on blank submit.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 2)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_8</t>
   </si>
   <si>
@@ -352,6 +456,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Counts as 1 of the 5 attempts before lockout (see TST_LOGI_TC_9) — never run it repeatedly on a shared account; use a disposable one or one whose counter resets on success.</t>
   </si>
   <si>
+    <t>Verified on Production: generic credentials error alert displayed on invalid password and user remains on /login.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 3)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_9</t>
   </si>
   <si>
@@ -361,7 +471,7 @@
     <t>TC_LOGIN_004 — Verify the account is temporarily locked after 5 consecutive failed login attempts</t>
   </si>
   <si>
-    <t>A registered, DISPOSABLE test account exists (not used by any other case). User is on the Log in page (homepage → "Log in").</t>
+    <t>A dedicated test account (cqatestuserforblockDND@mailsac.com) exists for lockout testing. User is on the Log in page (homepage → "Log in").</t>
   </si>
   <si>
     <t xml:space="preserve">1. Enter the account's e-mail with an incorrect password and click 'Log in'.
@@ -369,14 +479,20 @@
 3. Try a 6th time with the CORRECT password.</t>
   </si>
   <si>
-    <t>&lt;DISPOSABLE_ACCOUNT_EMAIL&gt;; wrong password ×5, then the correct password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
+    <t>cqatestuserforblockDND@mailsac.com; wrong password ×5, then the correct password. Passwords come from `{{env.*}}` tokens, never plaintext test data (ADR-023).</t>
   </si>
   <si>
     <t xml:space="preserve">1. Each of the first 5 attempts shows the 'check your login and password' alert referencing the 5-attempt limit.
-2. After the 5th failure the account is temporarily locked: the 6th attempt, even with the correct password, is rejected.</t>
-  </si>
-  <si>
-    <t>Source: OnboardingApp_Test_Plan.xlsx. LOCKS AN ACCOUNT — never a shared/pool account (migration plan Q10). Needs a disposable account per run (e.g. one created by the signup suite). Lockout duration and the exact 5th/6th-attempt copy are [ASSUMED] — not stated in the source.</t>
+2. After the 5th failure the account is temporarily locked for 2 minutes: the 6th attempt, even with the correct password, is rejected.</t>
+  </si>
+  <si>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Account is locked for 2 minutes on 5 consecutive wrong password attempts (user confirmed 2026-09-24). Uses dedicated test user cqatestuserforblockDND@mailsac.com.</t>
+  </si>
+  <si>
+    <t>Verified on Production: 5 consecutive failed login attempts show 5-attempt limit warning, and 6th attempt with valid password is rejected with account temporarily locked message.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 4)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_10</t>
@@ -403,6 +519,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. The existing TST_LOGI_TC_3 (login.test.js, not registered in C1TCRepository) only clicks the eye icon; this case asserts the field type. Automation reuses the click.</t>
   </si>
   <si>
+    <t>Verified on Production: password field type changes from password to text and back to password on clicking show password toggle.</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_4</t>
   </si>
   <si>
@@ -421,6 +540,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LOGI_TC_4 already clicks Forgotten your password and checks the reset page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: Forgotten your password link navigates to the reset password form.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 3)</t>
+  </si>
+  <si>
     <t>TST_LOGI_TC_6</t>
   </si>
   <si>
@@ -437,6 +562,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_LOGI_TC_6 already clicks Sign up on the login form and checks the page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking 'Don\'t have an account yet?' navigates to role selection screen (/regoptions).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 1 via TST_LOGI_TC_6)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_11</t>
@@ -465,6 +596,12 @@
     <t xml:space="preserve">NOT FOR AUTOMATION — marked YELLOW in the source plan (user, 2026-09-24): needs bulk-created username accounts; the first-login gate appears once per account. Manual execution only. Source: OnboardingApp_Test_Plan.xlsx. </t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Manual only — YELLOW in source (not for automation)</t>
   </si>
   <si>
@@ -539,6 +676,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Every admin suite already logs in this way (login.click_login_btn_schoolAdmin in their Before) but none asserts it as a case.</t>
+  </si>
+  <si>
+    <t>Verified on Production: school admin logs in through standard form and reaches /admin/admin/ dashboard.</t>
   </si>
   <si>
     <t>TST_LOGI_TC_15</t>
@@ -641,6 +781,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_APPS_TC_2 already clicks Log out (after TST_APPS_TC_1 opens the menu) and checks the landing page. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not. Knowledge: SOURCE saw logout land on /home OR /login?rurl=… — both are logged-out states; confirm which one the learner gets.</t>
   </si>
   <si>
+    <t>Verified on Production: logging out redirects to landing page with Log in and Sign up options.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 3 via TST_APPS_TC_1/2)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_6</t>
   </si>
   <si>
@@ -664,6 +810,12 @@
     <t xml:space="preserve">Source: OnboardingApp_Test_Plan.xlsx. </t>
   </si>
   <si>
+    <t>Verified on Production: submitting blank email displays 'This field is required' error message.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 3 via TST_RESE_TC_2)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_7</t>
   </si>
   <si>
@@ -686,6 +838,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. SENDS A REAL RESET E-MAIL to the account (harmless: the password only changes if the link is used). Use a Mailsac-inbox account, not a shared login.</t>
   </si>
   <si>
+    <t>Verified on Production: reset password confirmation screen displays heading "Reset password email sent" and informational body text for registered email.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB2Test_prod (Suite 1)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_8</t>
   </si>
   <si>
@@ -708,6 +866,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Legend 'Generic reset message': identical by design (no account enumeration), not a bug. 'No reset e-mail is actually sent' can only be checked in the Mailsac inbox.</t>
   </si>
   <si>
+    <t>Verified on Production: reset password confirmation screen displays identical generic heading "Reset password email sent" and informational body text for unregistered email (no account enumeration).</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_4</t>
   </si>
   <si>
@@ -724,6 +885,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_RESE_TC_4 already clicks Back to login and checks the login page is launched. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Back to login navigates back to the Login form.</t>
   </si>
   <si>
     <t>TST_RESE_TC_9</t>
@@ -752,6 +916,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CHANGES A REAL ACCOUNT'S PASSWORD — use a disposable account (e.g. one created by the signup suite in the same run), never a shared fixture. Mail handling as mailsacUI.openVerificationLink (sandboxed mail iframe, follow the link on the same page — c1-core-shared.md §A5/§B3). The reset link host may be the same login.comprodls.com host whose thor certificate is expired [ASSUMED — check].</t>
   </si>
   <si>
+    <t>Verified on Production: password reset requested, link extracted from Mailsac inbox, new password saved and confirmed via modal dialog, and user successfully logs in with new password.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 5)</t>
+  </si>
+  <si>
     <t>TST_RESE_TC_10</t>
   </si>
   <si>
@@ -779,6 +949,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. OVERLAP: the source's TC_FPWD_005 already ends with this login (its steps 5–6). Kept as its own row because the source has it; see Open items — the automation may compose LOGI_TC_1/2/5 with the new password instead of a new function.</t>
   </si>
   <si>
+    <t>Verified on Production: user logs out from active session, enters credentials with newly reset password on /login, and reaches role dashboard.</t>
+  </si>
+  <si>
     <t>TST_CREA_TC_31</t>
   </si>
   <si>
@@ -805,6 +978,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. First half of the source row; the student's first login with the temporary password is TST_LOGI_TC_18. CHANGES A REAL STUDENT'S PASSWORD — disposable student only. Module CREA = the teacher class page object (createNewClass.page.js); if Phase 1 finds the roster lives on another page object, re-code before automating. Confirmation copy after submit is [ASSUMED] (not in the source).</t>
+  </si>
+  <si>
+    <t>Verified on Production: Teacher opens class roster on Class data tab, locates student Actions menu, and verifies options to change password and manage student.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 8 via TST_CREA_TC_31)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_18</t>
@@ -830,7 +1009,7 @@
 3. The student can log in again with the new, self-set password.</t>
   </si>
   <si>
-    <t>Source: OnboardingApp_Test_Plan.xlsx. Serves BOTH TC_RESETPW_001 and TC_RESETPW_002 (same screen, different staff entry). Legend 'Password reset caveat': the same Gigya temporary-password screen-set as an Admin resetting their own password.</t>
+    <t>Source: OnboardingApp_Test_Plan.xlsx. Serves BOTH TC_RESETPW_001 and TC_RESETPW_002 (same screen, different staff entry). Out of automation scope per user instruction.</t>
   </si>
   <si>
     <t>TST_SPRF_TC_24</t>
@@ -861,6 +1040,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. [ASSUMED] entry point — the source's Legend says it was "taken from existing documentation … not independently re-verified live". OVERLAP to settle in Phase 1: the Students register already has TST_SPRF_TC_8 (admin sets a NEW password via View profile &gt; Manage account &gt; Password tab) and TST_SPRF_TC_23 (learner signs in with it). This row differs by the row Action Menu entry and the TEMPORARY-password first-login screen — confirm live that these are two different flows before automating. CHANGES A REAL STUDENT'S PASSWORD — disposable student only.</t>
   </si>
   <si>
+    <t>Verified on Production: School admin navigates to Learners tab, accesses learner profile, opens Manage learner profile, sets temporary password, and submits update.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 8 via TST_SPRF_TC_24)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_65</t>
   </si>
   <si>
@@ -880,6 +1065,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. onboarding.md §A1: Next is natively disabled until a role is picked (seen live, thor 2026-09-22).</t>
   </si>
   <si>
+    <t>Verified on Production: Learner, Teacher, and Parent role options are displayed with none pre-selected and Next button disabled.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 4)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_66</t>
   </si>
   <si>
@@ -905,6 +1096,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. The existing TST_SNUP_TC_59 checks the dialog NAMES the role and then continues; this case asserts the full copy and both buttons and stops at the dialog.</t>
   </si>
   <si>
+    <t>Verified on Production: modal dialog confirms selected role ('You have selected Teacher. Please check this is the right role') with 'Yes, continue' and 'No, go back' buttons.</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_67</t>
   </si>
   <si>
@@ -921,6 +1115,9 @@
     <t>The dialog closes, the user stays on the role-selection page and 'Teacher' is still selected.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking 'No, go back' closes dialog and retains previously selected role.</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_59</t>
   </si>
   <si>
@@ -943,6 +1140,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_SNUP_TC_59 already selects a role, checks the dialog names it, clicks Yes, continue and checks the role's next screen (data: role, expectedScreen) — run it for Parent too. Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
   </si>
   <si>
+    <t>Verified on Production: clicking 'Yes, continue' on confirmation dialog navigates to the role registration flow (Learner age gate).</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 5 via TST_SNUP_TC_69)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_68</t>
   </si>
   <si>
@@ -956,6 +1159,9 @@
   </si>
   <si>
     <t>The Log in form is shown.</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Login link on role selection page navigates to Login form.</t>
   </si>
   <si>
     <t>TST_SNUP_TC_69</t>
@@ -975,6 +1181,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. URL /learner-age-check (onboarding.md §A2). ⚠️ On thor the first-name box also reported visible on this screen (onboarding.md §A2) — check.</t>
+  </si>
+  <si>
+    <t>Verified on Production: learner age check screen (/learner-age-check) is displayed with Location field and Your age dropdown.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 5)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_70</t>
@@ -1004,6 +1216,9 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. Legend 'Learner age gate': India blocks 13–15 (source: confirmed live). Side-effect free.</t>
   </si>
   <si>
+    <t>Verified on Production: selecting underage (13-15) for India displays 'We\'re sorry' blocked screen and 'Go back' button.</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_71</t>
   </si>
   <si>
@@ -1028,6 +1243,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Legend 'Learner age gate': threshold is location-dependent — India blocks 13–15 / allows 16+; United Kingdom blocks 11–12 / allows 13+ (source: confirmed live). Boundary pairs worth adding in Phase 1: India 15/16, UK 12/13.</t>
+  </si>
+  <si>
+    <t>Verified on Production: age dropdown presents options (18+, 17 down to 5); age options verified on learner age check screen.</t>
   </si>
   <si>
     <t>TST_SNUP_TC_63</t>
@@ -1051,6 +1269,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. EXISTING TC reused (ADR-011 — no duplicate function): TST_SNUP_TC_63 already sets country + age and checks the learner profile form opens (LP setup chain). Phase 1: confirm it asserts this row's Expected Result; extend its assertion if it does not.</t>
+  </si>
+  <si>
+    <t>Verified on Production: selecting age 16+ (18+) with Location India allows user to proceed to the Learner registration profile form.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB1Test_prod (Suite 5 via TST_SNUP_TC_76 prerequisite)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_72</t>
@@ -1082,6 +1306,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Thor: the e-mail verification link host has an EXPIRED certificate (c1-core-shared.md §A4) — the verify step is blocked on thor until renewed; production works. New assertion = the locked, pre-filled Location. Account creation/verification reuse existing TST_SNUP_TC_60 (submit → pending screen), TST_SNUP_TC_61 (Mailsac link), TST_SNUP_TC_64 (learner welcome).</t>
   </si>
   <si>
+    <t>Verified on Production: Location is locked to pre-filled value from age check, user completes registration form, verifies account via Mailsac link, and successfully accesses Learner dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 2)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_76</t>
   </si>
   <si>
@@ -1107,6 +1337,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Side-effect free (never submits a valid form).</t>
+  </si>
+  <si>
+    <t>Verified on Production: required-field errors ('This field is required') displayed for First name and Last name on blank form submission.</t>
   </si>
   <si>
     <t>TST_SNUP_TC_73</t>
@@ -1136,6 +1369,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Thor: the e-mail verification link host has an EXPIRED certificate (c1-core-shared.md §A4) — the verify step is blocked on thor until renewed; production works. New assertion = the Teacher form's fields / no age gate. Creation and verification reuse existing TST_SNUP_TC_60, TST_SNUP_TC_61, TST_SNUP_TC_62 (tour + "Complete account set up").</t>
   </si>
   <si>
+    <t>Verified on Production: Teacher registration form opens directly with no age gate, user completes registration, verifies account via Mailsac link, and reaches Teacher dashboard / complete account setup prompt.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 3)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_77</t>
   </si>
   <si>
@@ -1165,6 +1404,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Side-effect free. Terms checkbox id differs by env (thor #legal-checkbox-1, prod #teacher-checkbox-1 — onboarding.md §A3).</t>
+  </si>
+  <si>
+    <t>Verified on Production: required-field errors ('This field is required') shown for First name, Last name, Location; 'E-mail address is invalid.' for Work email; 'Password does not meet complexity requirements' for weak password; Terms alert displayed when unchecked.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 1)</t>
   </si>
   <si>
     <t>TST_SNUP_TC_74</t>
@@ -1195,6 +1440,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Thor: the e-mail verification link host has an EXPIRED certificate (c1-core-shared.md §A4) — the verify step is blocked on thor until renewed; production works. Resolves onboarding.md §A2's [ASSUMED] Parent row. Creation/verification reuse TST_SNUP_TC_60/61; the parent dashboard assertion is new.</t>
   </si>
   <si>
+    <t>Verified on Production: Parent registration form includes age 18+ / guardian consent checkbox, user completes registration, verifies account via Mailsac link, and reaches Parent dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 4)</t>
+  </si>
+  <si>
     <t>TST_SNUP_TC_75</t>
   </si>
   <si>
@@ -1219,6 +1470,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Any message shown for the missing checkbox is not stated in the source — capture it verbatim in Phase 1 [ASSUMED]. Side-effect free if the form really does not submit; use a {{run.*}} e-mail anyway in case it does.</t>
+  </si>
+  <si>
+    <t>Verified on Production: Parent form does not submit without guardian consent, user remains on /register-parent, and parental checkbox highlights with error state (.parent-error).</t>
   </si>
   <si>
     <t>TST_PCHD_TC_1</t>
@@ -1252,6 +1506,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. PROPOSED module PCHD — no parent/child page object exists yet (migration plan U20, K19: the child form sits in a Gigya #child-iframe). CREATES A CHILD ACCOUNT. SOURCE reported child creation FAILING ON THOR [2026] — Phase 1 must check; if still failing, mark Blocked there (unblock: product fix or run on another env with the user's OK).</t>
   </si>
   <si>
+    <t>Verified on Production: Parent creates child account from 'My children', completes embedded panel details with consent checkbox, enters child username &amp; password, and receives account created confirmation with username.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test_prod (Suite 6)</t>
+  </si>
+  <si>
     <t>TST_PCHD_TC_2</t>
   </si>
   <si>
@@ -1272,6 +1532,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Exact inline error copy is not in the source — capture verbatim in Phase 1 [ASSUMED]. Side-effect free.</t>
+  </si>
+  <si>
+    <t>Verified on Production: on 'Create my child's account' blank submission displays required-field errors ('This field is required', 'This field is required (Month and Year)'), and form stays blocked on Subscreen 1 without ticking the consent checkbox.</t>
   </si>
   <si>
     <t>TST_PCHD_TC_3</t>
@@ -1299,6 +1562,9 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Depends on TST_PCHD_TC_1 in the same run.</t>
+  </si>
+  <si>
+    <t>Verified on Production: newly created child account logs in with username and password on /login, and successfully reaches the Learner dashboard ('Learner dashboard | Cambridge One').</t>
   </si>
   <si>
     <t>TST_INVI_TC_14</t>
@@ -1333,6 +1599,12 @@
     <t>Source: OnboardingApp_Test_Plan.xlsx. CREATES REAL DATA (a platform account) — ADR-021: needs the user's OK on a shared environment; place in a data-creating suite. Needs a teacher + class and an invite (reuse TST_CREA_TC_19–24 for the invite). Module INVI (invitation flow); if Phase 1 finds the invite signup form is the signup page object, re-code to SNUP before automating. Legend: invite signup has NO age gate.</t>
   </si>
   <si>
+    <t>Verified on Production: Teacher invites unregistered student, invitee opens 'View invite' link from Mailsac email, completes registration with prefilled email, verifies account via Mailsac, and reaches dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 7 via TST_INVI_TC_14)</t>
+  </si>
+  <si>
     <t>TST_INVI_TC_15</t>
   </si>
   <si>
@@ -1355,6 +1627,12 @@
   </si>
   <si>
     <t>Source: OnboardingApp_Test_Plan.xlsx. Existing INVI_TC_1–6 cover accepting the invite from the in-app bell; this is the e-mail link path. Each run leaves a pending invite in the class (migration plan Q4).</t>
+  </si>
+  <si>
+    <t>Verified on Production: Teacher invites registered learner, learner opens 'View invite' link while logged in, and lands directly on their learner dashboard.</t>
+  </si>
+  <si>
+    <t>Automated in onboardingB3Test (Suite 7 via TST_INVI_TC_15)</t>
   </si>
   <si>
     <t>TST_LOGI_TC_19</t>
@@ -1509,13 +1787,16 @@
   </si>
   <si>
     <t>Role: 'Parent' (source); data-driven for Teacher / Learner</t>
+  </si>
+  <si>
+    <t>Verified on Production: clicking Login link on Learner registration form returns user to Login page (/login).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1527,8 +1808,12 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF155724"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1538,6 +1823,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF3D1A66"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1563,7 +1853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1571,10 +1861,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1916,7 +2209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2017,14 +2310,14 @@
       <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -2032,46 +2325,46 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2079,46 +2372,46 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2126,13 +2419,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -2141,31 +2434,31 @@
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2173,13 +2466,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
@@ -2191,28 +2484,28 @@
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -2220,13 +2513,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
@@ -2238,28 +2531,28 @@
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -2267,13 +2560,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
@@ -2285,28 +2578,28 @@
         <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2314,13 +2607,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -2332,28 +2625,28 @@
         <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -2361,13 +2654,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
@@ -2379,28 +2672,28 @@
         <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2408,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>18</v>
@@ -2426,28 +2719,28 @@
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2455,13 +2748,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>18</v>
@@ -2473,28 +2766,28 @@
         <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2502,46 +2795,46 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2549,46 +2842,46 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2596,46 +2889,46 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2643,46 +2936,46 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -2690,46 +2983,46 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -2737,46 +3030,46 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -2784,13 +3077,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
@@ -2799,45 +3092,45 @@
         <v>19</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>22</v>
+        <v>157</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>136</v>
+      <c r="B20" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>18</v>
@@ -2846,45 +3139,45 @@
         <v>19</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>144</v>
+        <v>168</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>145</v>
+      <c r="B21" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>18</v>
@@ -2893,125 +3186,125 @@
         <v>19</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>149</v>
+        <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>144</v>
+        <v>176</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>152</v>
+      <c r="B22" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>144</v>
+        <v>185</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>160</v>
+      <c r="B23" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3019,107 +3312,107 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>177</v>
+      <c r="B25" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>176</v>
+        <v>142</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>184</v>
+      <c r="B26" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>18</v>
@@ -3128,45 +3421,45 @@
         <v>19</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>190</v>
+      <c r="B27" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>18</v>
@@ -3175,78 +3468,78 @@
         <v>19</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>197</v>
+      <c r="B28" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>22</v>
+        <v>233</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3254,46 +3547,46 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>208</v>
+        <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3301,46 +3594,46 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3348,46 +3641,46 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>22</v>
+        <v>256</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3395,46 +3688,46 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>91</v>
+        <v>266</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -3442,13 +3735,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>18</v>
@@ -3457,31 +3750,31 @@
         <v>19</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>236</v>
+        <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -3489,46 +3782,46 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>239</v>
+        <v>276</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>240</v>
+        <v>277</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>241</v>
+        <v>278</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>244</v>
+        <v>281</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>245</v>
+        <v>119</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>25</v>
+        <v>284</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -3536,46 +3829,46 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>250</v>
+        <v>289</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>253</v>
+        <v>292</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>25</v>
+        <v>284</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3583,93 +3876,93 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="M36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>25</v>
+        <v>303</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>262</v>
+      <c r="B37" s="4" t="s">
+        <v>304</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>263</v>
+        <v>305</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>267</v>
+        <v>310</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>27</v>
+        <v>185</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -3677,46 +3970,46 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>268</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="M38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>25</v>
+        <v>320</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -3724,46 +4017,46 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>25</v>
+        <v>328</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -3771,46 +4064,46 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>281</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>282</v>
+        <v>330</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>286</v>
+        <v>335</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>287</v>
+        <v>336</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>25</v>
+        <v>328</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -3818,13 +4111,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>288</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>290</v>
+        <v>340</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>18</v>
@@ -3833,31 +4126,31 @@
         <v>19</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>22</v>
+        <v>334</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>25</v>
+        <v>328</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -3865,46 +4158,46 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>22</v>
+        <v>348</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>297</v>
+        <v>349</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>25</v>
+        <v>352</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -3912,46 +4205,46 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>301</v>
+        <v>355</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>303</v>
+        <v>356</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>304</v>
+        <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>25</v>
+        <v>328</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -3959,46 +4252,46 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>309</v>
+        <v>361</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>310</v>
+        <v>18</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>311</v>
+        <v>362</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>312</v>
+        <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>314</v>
+        <v>364</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>25</v>
+        <v>366</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -4006,46 +4299,46 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>321</v>
+        <v>374</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>25</v>
+        <v>366</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -4053,46 +4346,46 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>323</v>
+        <v>377</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>18</v>
+        <v>379</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>326</v>
+        <v>380</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>327</v>
+        <v>381</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>328</v>
+        <v>382</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>329</v>
+        <v>383</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>25</v>
+        <v>366</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -4100,46 +4393,46 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>331</v>
+        <v>386</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>332</v>
+        <v>387</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>25</v>
+        <v>393</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -4147,46 +4440,46 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>338</v>
+        <v>395</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>339</v>
+        <v>396</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>271</v>
+        <v>397</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>25</v>
+        <v>403</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -4194,46 +4487,46 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>346</v>
+        <v>406</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>347</v>
+        <v>397</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>25</v>
+        <v>366</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -4241,46 +4534,46 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="M50" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -4288,46 +4581,46 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>360</v>
+        <v>422</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>362</v>
+        <v>424</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>364</v>
+        <v>426</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="M51" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>25</v>
+        <v>430</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -4335,46 +4628,46 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>368</v>
+        <v>432</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>369</v>
+        <v>433</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>371</v>
+        <v>434</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>373</v>
+        <v>436</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>25</v>
+        <v>439</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -4382,46 +4675,46 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>375</v>
+        <v>440</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>376</v>
+        <v>441</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>377</v>
+        <v>442</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>378</v>
+        <v>443</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>379</v>
+        <v>444</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>22</v>
+        <v>445</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>380</v>
+        <v>446</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="M53" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>25</v>
+        <v>430</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -4429,46 +4722,46 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>383</v>
+        <v>450</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>384</v>
+        <v>451</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>385</v>
+        <v>452</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>386</v>
+        <v>453</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>387</v>
+        <v>454</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>388</v>
+        <v>455</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>389</v>
+        <v>456</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M54" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>25</v>
+        <v>458</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -4476,46 +4769,46 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>390</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>391</v>
+        <v>460</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>392</v>
+        <v>461</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>393</v>
+        <v>462</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>394</v>
+        <v>463</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>396</v>
+        <v>464</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>397</v>
+        <v>465</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M55" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="M55" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>25</v>
+        <v>458</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4523,107 +4816,107 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>399</v>
+        <v>468</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>400</v>
+        <v>469</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>401</v>
+        <v>470</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>402</v>
+        <v>471</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M56" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="M56" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>25</v>
+        <v>458</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>406</v>
+      <c r="B57" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>408</v>
+        <v>478</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>479</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>409</v>
+        <v>480</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>22</v>
+        <v>481</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>410</v>
+        <v>482</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>183</v>
+        <v>483</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M57" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="M57" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>176</v>
+        <v>485</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>411</v>
+      <c r="B58" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>413</v>
+        <v>488</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>18</v>
@@ -4632,45 +4925,45 @@
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>271</v>
+        <v>489</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>414</v>
+        <v>490</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>22</v>
+        <v>491</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>415</v>
+        <v>492</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>183</v>
+        <v>493</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M58" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O58" s="4" t="s">
-        <v>176</v>
+        <v>495</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>416</v>
+      <c r="B59" s="5" t="s">
+        <v>496</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>417</v>
+        <v>497</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>418</v>
+        <v>498</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>18</v>
@@ -4679,45 +4972,45 @@
         <v>19</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>419</v>
+        <v>499</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>420</v>
+        <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>421</v>
+        <v>500</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O59" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="O59" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>422</v>
+      <c r="B60" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>423</v>
+        <v>502</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>424</v>
+        <v>503</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>18</v>
@@ -4726,45 +5019,45 @@
         <v>19</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>425</v>
+        <v>504</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>426</v>
+        <v>505</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O60" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>427</v>
+      <c r="B61" s="5" t="s">
+        <v>506</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>428</v>
+        <v>507</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>429</v>
+        <v>508</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>18</v>
@@ -4773,45 +5066,45 @@
         <v>19</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>430</v>
+        <v>332</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>431</v>
+        <v>509</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>432</v>
+        <v>510</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>433</v>
+        <v>511</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O61" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>434</v>
+      <c r="B62" s="5" t="s">
+        <v>512</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>435</v>
+        <v>513</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>436</v>
+        <v>514</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>18</v>
@@ -4820,45 +5113,45 @@
         <v>19</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>437</v>
+        <v>332</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>438</v>
+        <v>515</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>439</v>
+        <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>440</v>
+        <v>516</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O62" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="O62" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>441</v>
+      <c r="B63" s="5" t="s">
+        <v>517</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>442</v>
+        <v>518</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>18</v>
@@ -4867,45 +5160,45 @@
         <v>19</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>446</v>
+        <v>522</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O63" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>448</v>
+      <c r="B64" s="5" t="s">
+        <v>524</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>449</v>
+        <v>525</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>450</v>
+        <v>526</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>18</v>
@@ -4914,39 +5207,133 @@
         <v>19</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>291</v>
+        <v>528</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>452</v>
+        <v>529</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>292</v>
+        <v>530</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="M64" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="O64" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="O65" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N64" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>27</v>
+      <c r="N66" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="M10:M64">
+    <dataValidation type="list" allowBlank="1" sqref="M10:M66">
       <formula1>"Not Run,Pass,Fail,Blocked,On Hold"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M2:M64">
+    <dataValidation type="list" allowBlank="1" sqref="M2:M66">
       <formula1>"Not Run,Pass,Fail,Blocked,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
